--- a/src/sm4 auth.xlsx
+++ b/src/sm4 auth.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lahiru\BIT\Project 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lahiru\Java Spring\salesmanager4\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="47">
   <si>
     <t>Users</t>
   </si>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t xml:space="preserve"> approve</t>
-  </si>
-  <si>
-    <t>x only own</t>
   </si>
   <si>
     <t>grn</t>
@@ -526,7 +523,7 @@
         <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -1114,7 +1111,7 @@
         <v>11</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
@@ -1155,12 +1152,12 @@
         <v>11</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>11</v>
@@ -1238,7 +1235,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>11</v>
@@ -1301,7 +1298,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>19</v>
@@ -1312,7 +1309,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>19</v>
@@ -1323,7 +1320,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>11</v>
@@ -1331,7 +1328,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>11</v>
@@ -1339,7 +1336,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>11</v>
@@ -1347,7 +1344,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>11</v>
@@ -1355,7 +1352,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>11</v>
@@ -1366,7 +1363,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>11</v>
@@ -1377,7 +1374,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>11</v>
@@ -1388,7 +1385,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>11</v>
@@ -1432,7 +1429,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>11</v>
